--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10C90F-5DEE-C942-A4B7-88E74367ECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAA214E-6468-D24D-94E7-60323F5B7CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="30260" yWindow="2120" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -470,13 +470,13 @@
     <t>lab-08 &lt;br&gt; ae</t>
   </si>
   <si>
-    <t>ae-09 &lt;br&gt; lab-05</t>
-  </si>
-  <si>
     <t>lab-04 &lt;br&gt; ae-08</t>
   </si>
   <si>
-    <t>lab-05 &lt;br&gt; ae-09 &lt;br&gt; ae-10 &lt;br&gt; ae-11</t>
+    <t xml:space="preserve"> lab-05 &lt;br&gt; ae-09 &lt;br&gt; (thru II.3)</t>
+  </si>
+  <si>
+    <t>lab-05 &lt;br&gt; ae-09 &lt;br&gt; (thru II.3) &lt;br&gt; ae-10 &lt;br&gt; ae-11</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1127,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1144,7 +1144,7 @@
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1169,7 +1169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>54</v>
       </c>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAA214E-6468-D24D-94E7-60323F5B7CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794D16E7-5329-AF4D-98D5-6538A6EC68AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30260" yWindow="2120" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="146">
   <si>
     <t>WEEK</t>
   </si>
@@ -113,9 +113,6 @@
     <t>ae-10</t>
   </si>
   <si>
-    <t>ae-11</t>
-  </si>
-  <si>
     <t>[optional resource on map() from Advanced R](https://adv-r.hadley.nz/functionals.html?q=map#map)</t>
   </si>
   <si>
@@ -461,9 +458,6 @@
     <t>lab-03 &lt;br&gt; ae-06 &lt;br&gt; ae-07</t>
   </si>
   <si>
-    <t>thinking with data</t>
-  </si>
-  <si>
     <t xml:space="preserve">project proposal &lt;br&gt; lab-07 </t>
   </si>
   <si>
@@ -476,7 +470,10 @@
     <t xml:space="preserve"> lab-05 &lt;br&gt; ae-09 &lt;br&gt; (thru II.3)</t>
   </si>
   <si>
-    <t>lab-05 &lt;br&gt; ae-09 &lt;br&gt; (thru II.3) &lt;br&gt; ae-10 &lt;br&gt; ae-11</t>
+    <t>catch-up</t>
+  </si>
+  <si>
+    <t>lab-05 &lt;br&gt; ae-09 &lt;br&gt; (thru II.3) &lt;br&gt; ae-10</t>
   </si>
 </sst>
 </file>
@@ -886,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -903,18 +900,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -922,19 +919,19 @@
     </row>
     <row r="4" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -942,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -950,46 +947,46 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -997,27 +994,27 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>12</v>
@@ -1025,24 +1022,24 @@
     </row>
     <row r="12" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1050,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>11</v>
@@ -1058,10 +1055,10 @@
     </row>
     <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>18</v>
@@ -1072,13 +1069,13 @@
     </row>
     <row r="16" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>17</v>
@@ -1086,10 +1083,10 @@
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1097,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
@@ -1105,29 +1102,29 @@
     </row>
     <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1135,46 +1132,43 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1182,49 +1176,49 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1232,46 +1226,46 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1279,26 +1273,26 @@
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1306,7 +1300,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>20</v>
@@ -1314,26 +1308,26 @@
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1341,40 +1335,40 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1382,7 +1376,7 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>6</v>
@@ -1390,32 +1384,32 @@
     </row>
     <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1423,40 +1417,40 @@
         <v>13</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1464,40 +1458,40 @@
         <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1505,7 +1499,7 @@
         <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>7</v>
@@ -1513,32 +1507,32 @@
     </row>
     <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1546,13 +1540,13 @@
         <v>16</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794D16E7-5329-AF4D-98D5-6538A6EC68AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069F59F5-1923-264C-B41B-197C4614ACD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30260" yWindow="2120" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="29400" yWindow="500" windowWidth="36920" windowHeight="19920" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="147">
   <si>
     <t>WEEK</t>
   </si>
@@ -344,9 +344,6 @@
     <t>[functions - intro](https://mrne222-sp26.github.io/slides/13-functions-intro/13-functions-intro.html#1)</t>
   </si>
   <si>
-    <t>[git conflicts instructions](https://mrne222-sp26.github.io/slides/lab-07/lab-07-merge-conflicts.html) &lt;br&gt; [project guidelines](https://mrne222-sp26.github.io/website/03-project.html)</t>
-  </si>
-  <si>
     <t>[functions - details](https://mrne222-sp26.github.io/slides/15-functions-details/15-functions-details.html#1)</t>
   </si>
   <si>
@@ -401,9 +398,6 @@
     <t>*Spring break - no class*</t>
   </si>
   <si>
-    <t>lab-06 &lt;br&gt; ae</t>
-  </si>
-  <si>
     <t>lab-09 &lt;br&gt; ae</t>
   </si>
   <si>
@@ -419,9 +413,6 @@
     <t>[intro2r Ch 1 and 2](https://intro2r.com/)</t>
   </si>
   <si>
-    <t>sign up for project group</t>
-  </si>
-  <si>
     <t>[model checking and nonlinearity](https://enst222.github.io/slides/20-modeling-nonlinear-relationships/20-modeling-nonlinear-relationships#1)</t>
   </si>
   <si>
@@ -474,6 +465,18 @@
   </si>
   <si>
     <t>lab-05 &lt;br&gt; ae-09 &lt;br&gt; (thru II.3) &lt;br&gt; ae-10</t>
+  </si>
+  <si>
+    <t>[project interest form](https://forms.gle/6eJwhW7xYnbvjTs39)&lt;br&gt;[git conflicts instructions](https://mrne222-sp26.github.io/slides/lab-07/lab-07-merge-conflicts.html) &lt;br&gt; [project guidelines](https://mrne222-sp26.github.io/website/03-project.html)</t>
+  </si>
+  <si>
+    <t>ae-11</t>
+  </si>
+  <si>
+    <t>ae-12</t>
+  </si>
+  <si>
+    <t>ae-11&lt;br&gt;ae-12</t>
   </si>
 </sst>
 </file>
@@ -903,7 +906,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -922,16 +925,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -939,7 +942,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -953,7 +956,7 @@
         <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -961,7 +964,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -975,10 +978,10 @@
         <v>94</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -986,7 +989,7 @@
         <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -997,13 +1000,13 @@
         <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1011,7 +1014,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>96</v>
@@ -1025,13 +1028,13 @@
         <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1039,7 +1042,7 @@
         <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1058,7 +1061,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>18</v>
@@ -1075,7 +1078,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>17</v>
@@ -1086,7 +1089,7 @@
         <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1108,7 +1111,7 @@
         <v>98</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1124,7 +1127,7 @@
         <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1141,7 +1144,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1149,7 +1152,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1168,10 +1171,10 @@
         <v>53</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>7</v>
       </c>
@@ -1182,13 +1185,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1199,7 +1199,7 @@
         <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1207,10 +1207,10 @@
         <v>56</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1218,7 +1218,7 @@
         <v>57</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1229,7 +1229,7 @@
         <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1240,10 +1240,10 @@
         <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1254,10 +1254,10 @@
         <v>25</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1265,7 +1265,7 @@
         <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1276,7 +1276,7 @@
         <v>62</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1284,7 +1284,7 @@
         <v>63</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1292,7 +1292,7 @@
         <v>64</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1311,7 +1311,7 @@
         <v>66</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1319,7 +1319,7 @@
         <v>67</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1327,7 +1327,7 @@
         <v>68</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1338,7 +1338,7 @@
         <v>69</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1346,10 +1346,10 @@
         <v>70</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1360,7 +1360,7 @@
         <v>26</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1368,7 +1368,7 @@
         <v>72</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1387,10 +1387,10 @@
         <v>74</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1401,7 +1401,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1409,7 +1409,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1420,7 +1420,7 @@
         <v>77</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1428,10 +1428,10 @@
         <v>78</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1439,10 +1439,10 @@
         <v>79</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1450,7 +1450,7 @@
         <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1464,7 +1464,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1472,21 +1472,21 @@
         <v>82</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1513,7 +1513,7 @@
         <v>29</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1524,7 +1524,7 @@
         <v>28</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1532,7 +1532,7 @@
         <v>87</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069F59F5-1923-264C-B41B-197C4614ACD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEED2E44-AB4B-EB4A-83C9-6B46898BFA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="36920" windowHeight="19920" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="150">
   <si>
     <t>WEEK</t>
   </si>
@@ -477,6 +477,15 @@
   </si>
   <si>
     <t>ae-11&lt;br&gt;ae-12</t>
+  </si>
+  <si>
+    <t>ae-13</t>
+  </si>
+  <si>
+    <t>ae-14</t>
+  </si>
+  <si>
+    <t>ae-13 &lt;br&gt; ae-14</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1252,7 @@
         <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1257,7 +1266,7 @@
         <v>104</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1265,7 +1274,7 @@
         <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEED2E44-AB4B-EB4A-83C9-6B46898BFA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4AD168-1CEB-6646-97FD-EC543D896351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="30120" yWindow="500" windowWidth="35640" windowHeight="20020" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="154">
   <si>
     <t>WEEK</t>
   </si>
@@ -383,9 +383,6 @@
     <t>project proposal peer review</t>
   </si>
   <si>
-    <t>lab-09</t>
-  </si>
-  <si>
     <t>TBD</t>
   </si>
   <si>
@@ -449,9 +446,6 @@
     <t>lab-03 &lt;br&gt; ae-06 &lt;br&gt; ae-07</t>
   </si>
   <si>
-    <t xml:space="preserve">project proposal &lt;br&gt; lab-07 </t>
-  </si>
-  <si>
     <t>lab-08 &lt;br&gt; ae</t>
   </si>
   <si>
@@ -486,6 +480,24 @@
   </si>
   <si>
     <t>ae-13 &lt;br&gt; ae-14</t>
+  </si>
+  <si>
+    <t>ae-15</t>
+  </si>
+  <si>
+    <t>ae-16</t>
+  </si>
+  <si>
+    <t>ae-17</t>
+  </si>
+  <si>
+    <t>ae-18</t>
+  </si>
+  <si>
+    <t>ae-15 &lt;br&gt; ae-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project proposal </t>
   </si>
 </sst>
 </file>
@@ -934,16 +946,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -951,7 +963,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -965,7 +977,7 @@
         <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -973,7 +985,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -990,7 +1002,7 @@
         <v>106</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1009,13 +1021,13 @@
         <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1023,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>96</v>
@@ -1037,7 +1049,7 @@
         <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>97</v>
@@ -1051,7 +1063,7 @@
         <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1070,7 +1082,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>18</v>
@@ -1087,7 +1099,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>17</v>
@@ -1098,7 +1110,7 @@
         <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1136,7 +1148,7 @@
         <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1153,7 +1165,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1161,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1180,7 +1192,7 @@
         <v>53</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1194,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>19</v>
@@ -1208,7 +1220,7 @@
         <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1219,7 +1231,7 @@
         <v>102</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1227,7 +1239,7 @@
         <v>57</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1252,7 +1264,7 @@
         <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1266,7 +1278,7 @@
         <v>104</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1274,7 +1286,7 @@
         <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1285,7 +1297,7 @@
         <v>62</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1293,7 +1305,7 @@
         <v>63</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1301,7 +1313,7 @@
         <v>64</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1311,8 +1323,8 @@
       <c r="B37" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>20</v>
+      <c r="D37" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1336,7 +1348,7 @@
         <v>68</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1358,7 +1370,7 @@
         <v>105</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1369,7 +1381,7 @@
         <v>26</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1377,7 +1389,7 @@
         <v>72</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1388,7 +1400,7 @@
         <v>73</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1396,10 +1408,10 @@
         <v>74</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1410,7 +1422,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1418,7 +1430,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1429,7 +1441,7 @@
         <v>77</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1437,7 +1449,7 @@
         <v>78</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>113</v>
@@ -1448,7 +1460,7 @@
         <v>79</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>113</v>
@@ -1459,7 +1471,7 @@
         <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1473,7 +1485,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1481,7 +1493,7 @@
         <v>82</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>113</v>
@@ -1492,7 +1504,7 @@
         <v>112</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>113</v>
@@ -1541,7 +1553,7 @@
         <v>87</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4AD168-1CEB-6646-97FD-EC543D896351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D12640-AB41-C14F-BCF0-10F518A6D3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30120" yWindow="500" windowWidth="35640" windowHeight="20020" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="140" yWindow="500" windowWidth="26220" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="154">
   <si>
     <t>WEEK</t>
   </si>
@@ -395,9 +395,6 @@
     <t>*Spring break - no class*</t>
   </si>
   <si>
-    <t>lab-09 &lt;br&gt; ae</t>
-  </si>
-  <si>
     <t>project report for peer review</t>
   </si>
   <si>
@@ -485,19 +482,22 @@
     <t>ae-15</t>
   </si>
   <si>
-    <t>ae-16</t>
-  </si>
-  <si>
-    <t>ae-17</t>
-  </si>
-  <si>
-    <t>ae-18</t>
-  </si>
-  <si>
     <t>ae-15 &lt;br&gt; ae-16</t>
   </si>
   <si>
     <t xml:space="preserve">project proposal </t>
+  </si>
+  <si>
+    <t>ae-17 #1-7</t>
+  </si>
+  <si>
+    <t>ae-17 #8-13</t>
+  </si>
+  <si>
+    <t>lab-07 &lt;br&gt; ae-17</t>
+  </si>
+  <si>
+    <t>ae-16 (skip 4b-d and 6b-d)</t>
   </si>
 </sst>
 </file>
@@ -946,16 +946,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -963,7 +963,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -977,7 +977,7 @@
         <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -985,7 +985,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1002,7 +1002,7 @@
         <v>106</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1021,13 +1021,13 @@
         <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1035,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>96</v>
@@ -1049,7 +1049,7 @@
         <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>97</v>
@@ -1063,7 +1063,7 @@
         <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1082,7 +1082,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>17</v>
@@ -1110,7 +1110,7 @@
         <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1148,7 +1148,7 @@
         <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1165,7 +1165,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1192,7 +1192,7 @@
         <v>53</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1206,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>19</v>
@@ -1220,7 +1220,7 @@
         <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1231,7 +1231,7 @@
         <v>102</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1239,7 +1239,7 @@
         <v>57</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1264,7 +1264,7 @@
         <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1278,7 +1278,7 @@
         <v>104</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1286,7 +1286,7 @@
         <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1348,7 +1348,7 @@
         <v>68</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1370,7 +1370,7 @@
         <v>105</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1381,7 +1381,7 @@
         <v>26</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1389,7 +1389,7 @@
         <v>72</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1408,7 +1408,7 @@
         <v>74</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>150</v>
@@ -1430,7 +1430,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1440,6 +1440,9 @@
       <c r="B49" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="D49" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="E49" s="1" t="s">
         <v>6</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1485,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D12640-AB41-C14F-BCF0-10F518A6D3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A8EACE-0075-6643-B242-27A3CD3C57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="500" windowWidth="26220" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="155">
   <si>
     <t>WEEK</t>
   </si>
@@ -56,9 +56,6 @@
     <t>ae-01</t>
   </si>
   <si>
-    <t>lab-08</t>
-  </si>
-  <si>
     <t>project work</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>[models with multiple predictors](https://enst222.github.io/slides/21-model-multiple-predictors/21-model-multiple-predictors#1)</t>
   </si>
   <si>
-    <t xml:space="preserve">spatial data: make a map </t>
-  </si>
-  <si>
     <t>[tying up loose ends](https://enst222.github.io/slides/23-tying-up-loose-ends/23-tying-up-loose-ends#1)</t>
   </si>
   <si>
@@ -443,9 +437,6 @@
     <t>lab-03 &lt;br&gt; ae-06 &lt;br&gt; ae-07</t>
   </si>
   <si>
-    <t>lab-08 &lt;br&gt; ae</t>
-  </si>
-  <si>
     <t>lab-04 &lt;br&gt; ae-08</t>
   </si>
   <si>
@@ -498,6 +489,18 @@
   </si>
   <si>
     <t>ae-16 (skip 4b-d and 6b-d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lab-08b </t>
+  </si>
+  <si>
+    <t>stepwise model selection and project work</t>
+  </si>
+  <si>
+    <t>maps in R and project work</t>
+  </si>
+  <si>
+    <t>lab-08b</t>
   </si>
 </sst>
 </file>
@@ -907,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -924,18 +927,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -943,19 +946,19 @@
     </row>
     <row r="4" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -963,7 +966,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -971,46 +974,46 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1018,52 +1021,52 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1071,46 +1074,46 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1118,37 +1121,37 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1156,43 +1159,43 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1200,46 +1203,46 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1247,46 +1250,46 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1294,26 +1297,26 @@
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1321,34 +1324,34 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1356,40 +1359,40 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1397,40 +1400,40 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1438,43 +1441,34 @@
         <v>13</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1482,40 +1476,43 @@
         <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1523,40 +1520,40 @@
         <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1564,13 +1561,13 @@
         <v>16</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A8EACE-0075-6643-B242-27A3CD3C57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763F57F-011E-4345-BEAB-C7F61E32FDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="500" windowWidth="26220" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">lab-08b </t>
   </si>
   <si>
-    <t>stepwise model selection and project work</t>
-  </si>
-  <si>
     <t>maps in R and project work</t>
   </si>
   <si>
     <t>lab-08b</t>
+  </si>
+  <si>
+    <t>[models with multiple numeric predictors](https://mrne222-sp26.github.io/slides/22-more-mult-predictors/22-more-mult-predictors.html#1) and project work</t>
   </si>
 </sst>
 </file>
@@ -1444,15 +1444,15 @@
         <v>75</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1460,7 +1460,7 @@
         <v>77</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763F57F-011E-4345-BEAB-C7F61E32FDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45D0182-3AE4-3C42-B7BB-B09133C7B3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="500" windowWidth="26220" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="31440" yWindow="1420" windowWidth="26220" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t>[models with multiple predictors](https://enst222.github.io/slides/21-model-multiple-predictors/21-model-multiple-predictors#1)</t>
   </si>
   <si>
-    <t>[tying up loose ends](https://enst222.github.io/slides/23-tying-up-loose-ends/23-tying-up-loose-ends#1)</t>
-  </si>
-  <si>
     <t>final project</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
     <t>project proposal peer review</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t xml:space="preserve">ae </t>
   </si>
   <si>
@@ -494,13 +488,19 @@
     <t xml:space="preserve">lab-08b </t>
   </si>
   <si>
-    <t>maps in R and project work</t>
-  </si>
-  <si>
     <t>lab-08b</t>
   </si>
   <si>
     <t>[models with multiple numeric predictors](https://mrne222-sp26.github.io/slides/22-more-mult-predictors/22-more-mult-predictors.html#1) and project work</t>
+  </si>
+  <si>
+    <t>[tying up loose ends](https://enst222.github.io/slides/23-tying-up-loose-ends/23-tying-up-loose-ends#1) and project work</t>
+  </si>
+  <si>
+    <t>Maps in R</t>
+  </si>
+  <si>
+    <t>Spatial analysis</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
@@ -927,18 +927,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -946,19 +946,19 @@
     </row>
     <row r="4" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -966,7 +966,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -974,46 +974,46 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1021,27 +1021,27 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>11</v>
@@ -1049,24 +1049,24 @@
     </row>
     <row r="12" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1074,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>10</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>17</v>
@@ -1096,13 +1096,13 @@
     </row>
     <row r="16" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1121,7 +1121,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>12</v>
@@ -1129,29 +1129,29 @@
     </row>
     <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1159,29 +1159,29 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>22</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1203,13 +1203,13 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>18</v>
@@ -1217,32 +1217,32 @@
     </row>
     <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1250,46 +1250,46 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1297,26 +1297,26 @@
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1324,34 +1324,34 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1359,40 +1359,40 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>19</v>
@@ -1408,32 +1408,32 @@
     </row>
     <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1441,23 +1441,23 @@
         <v>13</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>152</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1476,43 +1476,43 @@
         <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1520,40 +1520,40 @@
         <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1561,13 +1561,13 @@
         <v>16</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45D0182-3AE4-3C42-B7BB-B09133C7B3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5957AC94-EDBB-544F-AB27-EFA353E50BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31440" yWindow="1420" windowWidth="26220" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="158">
   <si>
     <t>WEEK</t>
   </si>
@@ -368,15 +368,9 @@
     <t>Th Apr 23</t>
   </si>
   <si>
-    <t>ae</t>
-  </si>
-  <si>
     <t>project proposal peer review</t>
   </si>
   <si>
-    <t xml:space="preserve">ae </t>
-  </si>
-  <si>
     <t>*Spring break - no lab*</t>
   </si>
   <si>
@@ -501,6 +495,21 @@
   </si>
   <si>
     <t>Spatial analysis</t>
+  </si>
+  <si>
+    <t>ae-18</t>
+  </si>
+  <si>
+    <t>ae-19</t>
+  </si>
+  <si>
+    <t>ae-20</t>
+  </si>
+  <si>
+    <t>ae-20 (cont.)</t>
+  </si>
+  <si>
+    <t>ae-18 &lt;br&gt; ae-19</t>
   </si>
 </sst>
 </file>
@@ -949,16 +958,16 @@
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -966,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -980,7 +989,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -988,7 +997,7 @@
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1005,7 +1014,7 @@
         <v>103</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1024,13 +1033,13 @@
         <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1038,7 +1047,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>93</v>
@@ -1052,7 +1061,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>94</v>
@@ -1066,7 +1075,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1085,7 +1094,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>17</v>
@@ -1102,7 +1111,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
@@ -1113,7 +1122,7 @@
         <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1151,7 +1160,7 @@
         <v>46</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1168,7 +1177,7 @@
         <v>96</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1176,7 +1185,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1195,7 +1204,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1209,7 +1218,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>18</v>
@@ -1223,7 +1232,7 @@
         <v>98</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1234,7 +1243,7 @@
         <v>99</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1242,7 +1251,7 @@
         <v>54</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1267,7 +1276,7 @@
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1281,7 +1290,7 @@
         <v>101</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1289,7 +1298,7 @@
         <v>58</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1300,7 +1309,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1308,7 +1317,7 @@
         <v>60</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1316,7 +1325,7 @@
         <v>61</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1351,7 +1360,7 @@
         <v>65</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1362,7 +1371,7 @@
         <v>66</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1373,7 +1382,7 @@
         <v>102</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1384,7 +1393,7 @@
         <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1392,7 +1401,7 @@
         <v>69</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1411,10 +1420,10 @@
         <v>71</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1425,7 +1434,7 @@
         <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1433,7 +1442,7 @@
         <v>73</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1444,7 +1453,7 @@
         <v>74</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1452,7 +1461,7 @@
         <v>75</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1460,7 +1469,7 @@
         <v>76</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1468,7 +1477,7 @@
         <v>77</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1482,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1490,10 +1499,10 @@
         <v>79</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1501,10 +1510,10 @@
         <v>109</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1512,7 +1521,7 @@
         <v>80</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1531,10 +1540,10 @@
         <v>82</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1542,10 +1551,10 @@
         <v>83</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1553,7 +1562,7 @@
         <v>84</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5957AC94-EDBB-544F-AB27-EFA353E50BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC37C2A-3B9B-8249-B2B0-96B3F93ABC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>project work</t>
   </si>
   <si>
-    <t>project peer review</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLIDES </t>
   </si>
   <si>
@@ -510,6 +507,9 @@
   </si>
   <si>
     <t>ae-18 &lt;br&gt; ae-19</t>
+  </si>
+  <si>
+    <t>project  peer review</t>
   </si>
 </sst>
 </file>
@@ -919,10 +919,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -936,18 +936,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -955,19 +955,19 @@
     </row>
     <row r="4" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -975,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -983,46 +983,46 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1030,52 +1030,52 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1083,46 +1083,46 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1130,37 +1130,37 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1168,43 +1168,43 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1212,46 +1212,46 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1259,46 +1259,46 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1306,26 +1306,26 @@
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1333,34 +1333,34 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1368,40 +1368,40 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1409,40 +1409,40 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1450,34 +1450,34 @@
         <v>13</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1485,43 +1485,43 @@
         <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1529,40 +1529,40 @@
         <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>6</v>
+        <v>80</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1570,13 +1570,13 @@
         <v>16</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/Teaching/MRNE222-sp26/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC37C2A-3B9B-8249-B2B0-96B3F93ABC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D6829E-366E-924A-9A39-9126A9748799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{C5F9D553-35B7-894D-9EDC-9F93DB09BC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="155">
   <si>
     <t>WEEK</t>
   </si>
@@ -287,15 +287,9 @@
     <t>Th Apr 30</t>
   </si>
   <si>
-    <t>F May 1</t>
-  </si>
-  <si>
     <t>Th May 7</t>
   </si>
   <si>
-    <t>7:00-9:15 (final exam period) [Project review panel](https://docs.google.com/spreadsheets/d/1sOsSmirVyEtzoimN0hAnRj5oGKDhhY_Y1c1nvY7owSs/edit?usp=sharing)</t>
-  </si>
-  <si>
     <t>RESOURCES</t>
   </si>
   <si>
@@ -500,16 +494,13 @@
     <t>ae-19</t>
   </si>
   <si>
-    <t>ae-20</t>
-  </si>
-  <si>
-    <t>ae-20 (cont.)</t>
-  </si>
-  <si>
     <t>ae-18 &lt;br&gt; ae-19</t>
   </si>
   <si>
     <t>project  peer review</t>
+  </si>
+  <si>
+    <t>[survey](https://forms.gle/P2LhiWzTcnMNrQHr5)</t>
   </si>
 </sst>
 </file>
@@ -900,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA2A9EF-AA31-554C-9B9C-A68FEC593FBF}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -919,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>7</v>
@@ -939,7 +930,7 @@
         <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -947,7 +938,7 @@
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -958,16 +949,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -975,7 +966,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -986,10 +977,10 @@
         <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -997,7 +988,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1008,13 +999,13 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1022,7 +1013,7 @@
         <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1033,13 +1024,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1047,10 +1038,10 @@
         <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>10</v>
@@ -1061,13 +1052,13 @@
         <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1075,7 +1066,7 @@
         <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1094,7 +1085,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>16</v>
@@ -1111,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>15</v>
@@ -1122,7 +1113,7 @@
         <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1141,10 +1132,10 @@
         <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1152,7 +1143,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1160,7 +1151,7 @@
         <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1174,10 +1165,10 @@
         <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1185,7 +1176,7 @@
         <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1204,7 +1195,7 @@
         <v>49</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1218,7 +1209,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>17</v>
@@ -1229,10 +1220,10 @@
         <v>51</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1240,10 +1231,10 @@
         <v>52</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1251,7 +1242,7 @@
         <v>53</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1262,7 +1253,7 @@
         <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1273,10 +1264,10 @@
         <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1287,10 +1278,10 @@
         <v>23</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1298,7 +1289,7 @@
         <v>57</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1309,7 +1300,7 @@
         <v>58</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1317,7 +1308,7 @@
         <v>59</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1325,7 +1316,7 @@
         <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1336,7 +1327,7 @@
         <v>61</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1344,7 +1335,7 @@
         <v>62</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1352,7 +1343,7 @@
         <v>63</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1360,7 +1351,7 @@
         <v>64</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1371,7 +1362,7 @@
         <v>65</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1379,10 +1370,10 @@
         <v>66</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1393,7 +1384,7 @@
         <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1401,7 +1392,7 @@
         <v>68</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1420,10 +1411,10 @@
         <v>70</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1434,7 +1425,7 @@
         <v>25</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1442,7 +1433,7 @@
         <v>72</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1453,7 +1444,7 @@
         <v>73</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1461,7 +1452,7 @@
         <v>74</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -1469,7 +1460,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1477,7 +1468,7 @@
         <v>76</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1491,7 +1482,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1499,21 +1490,21 @@
         <v>78</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1521,7 +1512,7 @@
         <v>79</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1532,7 +1523,7 @@
         <v>80</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1540,42 +1531,28 @@
         <v>81</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>16</v>
+      </c>
       <c r="B60" s="1" t="s">
         <v>83</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A61" s="1">
-        <v>16</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F61" s="1" t="s">
         <v>26</v>
       </c>
     </row>
